--- a/diseases/d001/1995-1999.xlsx
+++ b/diseases/d001/1995-1999.xlsx
@@ -1943,6 +1943,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2327,6 +2332,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2472,6 +2482,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2617,6 +2632,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2762,6 +2782,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2907,6 +2932,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3052,6 +3082,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3197,6 +3232,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3342,6 +3382,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3487,6 +3532,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3632,6 +3682,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3777,6 +3832,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4312,6 +4372,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4696,6 +4761,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4841,6 +4911,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4986,6 +5061,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5131,6 +5211,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5276,6 +5361,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5421,6 +5511,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5566,6 +5661,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5711,6 +5811,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5856,6 +5961,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6001,6 +6111,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6146,6 +6261,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6681,6 +6801,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7065,6 +7190,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7210,6 +7340,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7355,6 +7490,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7500,6 +7640,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7645,6 +7790,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7790,6 +7940,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7935,6 +8090,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8080,6 +8240,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8225,6 +8390,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8370,6 +8540,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8513,6 +8688,11 @@
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">

--- a/diseases/d001/1995-1999.xlsx
+++ b/diseases/d001/1995-1999.xlsx
@@ -1938,11 +1938,6 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1955,22 +1950,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -2036,17 +2021,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2071,12 +2056,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1997-02-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1997-02</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2085,170 +2070,66 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Svarti dauði</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="Q9" t="n">
+        <v>0</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>SER_IS_ECDC_PLAG_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -2310,12 +2191,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1997-02-01</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2327,11 +2208,6 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2344,22 +2220,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2460,12 +2326,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
+          <t>1997-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2477,11 +2343,6 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2494,22 +2355,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2610,12 +2461,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1997-04-01</t>
+          <t>1997-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2627,11 +2478,6 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2644,22 +2490,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2760,12 +2596,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1997-05-01</t>
+          <t>1997-06-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2777,11 +2613,6 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2794,22 +2625,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2910,12 +2731,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1997-06-01</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2927,11 +2748,6 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2944,22 +2760,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -3060,12 +2866,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
+          <t>1997-08-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3077,11 +2883,6 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3094,22 +2895,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3210,12 +3001,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1997-08-01</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3227,11 +3018,6 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3244,22 +3030,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3360,12 +3136,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
+          <t>1997-10-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3377,11 +3153,6 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3394,22 +3165,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3510,12 +3271,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1997-10-01</t>
+          <t>1997-11-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3527,11 +3288,6 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3544,22 +3300,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3660,12 +3406,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1997-11-01</t>
+          <t>1997-12-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3677,11 +3423,6 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3694,22 +3435,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3780,12 +3511,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3810,12 +3541,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3824,81 +3555,87 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3662,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3974,20 +3711,98 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
         </is>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN21" t="b">
+        <v>1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -4081,17 +3896,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4130,165 +3945,66 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="Q22" t="n">
+        <v>0</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN22" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4350,12 +4066,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1998-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1998-02</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4367,11 +4083,6 @@
       <c r="Q23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4384,22 +4095,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4465,17 +4166,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4500,12 +4201,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1998-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1998-03</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4514,170 +4215,66 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Svarti dauði</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="Q24" t="n">
+        <v>0</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN24" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>SER_IS_ECDC_PLAG_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4336,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1998-02-01</t>
+          <t>1998-04-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1998-02</t>
+          <t>1998-04</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4756,11 +4353,6 @@
       <c r="Q25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4773,22 +4365,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4889,12 +4471,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1998-03-01</t>
+          <t>1998-05-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1998-03</t>
+          <t>1998-05</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4906,11 +4488,6 @@
       <c r="Q26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4923,22 +4500,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -5039,12 +4606,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1998-04-01</t>
+          <t>1998-06-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1998-04</t>
+          <t>1998-06</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -5056,11 +4623,6 @@
       <c r="Q27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5073,22 +4635,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -5189,12 +4741,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1998-05-01</t>
+          <t>1998-07-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1998-05</t>
+          <t>1998-07</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -5206,11 +4758,6 @@
       <c r="Q28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5223,22 +4770,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5339,12 +4876,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1998-08-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1998-06</t>
+          <t>1998-08</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5356,11 +4893,6 @@
       <c r="Q29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5373,22 +4905,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5489,12 +5011,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1998-07-01</t>
+          <t>1998-09-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1998-07</t>
+          <t>1998-09</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5506,11 +5028,6 @@
       <c r="Q30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5523,22 +5040,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5639,12 +5146,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1998-08-01</t>
+          <t>1998-10-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1998-08</t>
+          <t>1998-10</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5656,11 +5163,6 @@
       <c r="Q31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5673,22 +5175,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5789,12 +5281,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1998-09-01</t>
+          <t>1998-11-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1998-09</t>
+          <t>1998-11</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5806,11 +5298,6 @@
       <c r="Q32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5823,22 +5310,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5939,12 +5416,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1998-10-01</t>
+          <t>1998-12-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1998-10</t>
+          <t>1998-12</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5956,11 +5433,6 @@
       <c r="Q33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5973,22 +5445,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -6059,12 +5521,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6089,12 +5551,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1998-11-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1998-11</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -6103,81 +5565,87 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6204,17 +5672,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6239,12 +5707,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1998-12</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -6253,81 +5721,165 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6359,12 +5911,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6403,87 +5955,66 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
+      <c r="Q36" t="n">
+        <v>0</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6510,17 +6041,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6545,12 +6076,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6559,165 +6090,66 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="Q37" t="n">
+        <v>0</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN37" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6211,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6796,11 +6228,6 @@
       <c r="Q38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6813,22 +6240,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6894,17 +6311,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6929,12 +6346,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6943,170 +6360,66 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Svarti dauði</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="Q39" t="n">
+        <v>0</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN39" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr">
-        <is>
-          <t>SER_IS_ECDC_PLAG_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7168,12 +6481,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -7185,11 +6498,6 @@
       <c r="Q40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7202,22 +6510,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -7318,12 +6616,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -7335,11 +6633,6 @@
       <c r="Q41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7352,22 +6645,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7468,12 +6751,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -7485,11 +6768,6 @@
       <c r="Q42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7502,22 +6780,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7618,12 +6886,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7635,11 +6903,6 @@
       <c r="Q43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7652,22 +6915,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7768,12 +7021,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7785,11 +7038,6 @@
       <c r="Q44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7802,22 +7050,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7918,12 +7156,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7935,11 +7173,6 @@
       <c r="Q45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7952,22 +7185,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -8068,12 +7291,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-11-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-11</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -8085,11 +7308,6 @@
       <c r="Q46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8102,22 +7320,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -8218,12 +7426,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-12-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-12</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -8235,11 +7443,6 @@
       <c r="Q47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8252,23 +7455,13 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -8305,456 +7498,6 @@
         </is>
       </c>
       <c r="BC47" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>D001</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>plague</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>D001</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>鼠疫</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>1999-10-01</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>1999-10</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP48" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV48" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA48" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB48" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC48" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>D001</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>plague</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>D001</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>鼠疫</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>1999-11-01</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>1999-11</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV49" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA49" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB49" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC49" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>D001</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>plague</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>D001</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>鼠疫</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>1999-12-01</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>1999-12</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP50" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
-      <c r="AT50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV50" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA50" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB50" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC50" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -8886,7 +7629,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -8906,7 +7649,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -8916,7 +7659,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d001/1995-1999.xlsx
+++ b/diseases/d001/1995-1999.xlsx
@@ -2021,17 +2021,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1997-02-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2070,66 +2070,170 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Svarti dauði</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>0</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_PLAG_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2295,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
+          <t>1997-02-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1997-02</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2326,12 +2430,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1997-04-01</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2461,12 +2565,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1997-05-01</t>
+          <t>1997-04-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2596,12 +2700,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1997-06-01</t>
+          <t>1997-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2731,12 +2835,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
+          <t>1997-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2866,12 +2970,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1997-08-01</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3001,12 +3105,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
+          <t>1997-08-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3136,12 +3240,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1997-10-01</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3271,12 +3375,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1997-11-01</t>
+          <t>1997-10-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3406,12 +3510,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-11-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3511,12 +3615,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3541,12 +3645,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-12-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3555,87 +3659,66 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
+      <c r="Q20" t="n">
+        <v>0</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3745,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3711,98 +3794,20 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN21" t="b">
-        <v>1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -3896,17 +3901,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3945,66 +3950,165 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN22" t="b">
+        <v>1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4066,12 +4170,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1998-02-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1998-02</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4166,17 +4270,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4201,12 +4305,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1998-03-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1998-03</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4215,66 +4319,170 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Svarti dauði</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN24" t="b">
+        <v>0</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_PLAG_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4336,12 +4544,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1998-04-01</t>
+          <t>1998-02-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1998-04</t>
+          <t>1998-02</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4471,12 +4679,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1998-05-01</t>
+          <t>1998-03-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1998-05</t>
+          <t>1998-03</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4606,12 +4814,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1998-04-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1998-06</t>
+          <t>1998-04</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4741,12 +4949,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1998-07-01</t>
+          <t>1998-05-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1998-07</t>
+          <t>1998-05</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4876,12 +5084,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1998-08-01</t>
+          <t>1998-06-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1998-08</t>
+          <t>1998-06</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5011,12 +5219,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1998-09-01</t>
+          <t>1998-07-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1998-09</t>
+          <t>1998-07</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5146,12 +5354,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1998-10-01</t>
+          <t>1998-08-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1998-10</t>
+          <t>1998-08</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5281,12 +5489,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1998-11-01</t>
+          <t>1998-09-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1998-11</t>
+          <t>1998-09</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5416,12 +5624,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-10-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1998-12</t>
+          <t>1998-10</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5521,12 +5729,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5551,12 +5759,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-11-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-11</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5565,87 +5773,66 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
+      <c r="Q34" t="n">
+        <v>0</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5672,17 +5859,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5707,12 +5894,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-12-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-12</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5721,165 +5908,66 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="Q35" t="n">
+        <v>0</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5911,12 +5999,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5955,66 +6043,87 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6041,17 +6150,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6076,12 +6185,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6090,66 +6199,165 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN37" t="b">
+        <v>1</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D89_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6419,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6311,17 +6519,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6346,12 +6554,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6360,66 +6568,170 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_PLAGUE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Svarti dauði</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>0</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_PLAG_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6481,12 +6793,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6616,12 +6928,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6751,12 +7063,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6886,12 +7198,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7021,12 +7333,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7156,12 +7468,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7291,12 +7603,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7426,12 +7738,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7498,6 +7810,411 @@
         </is>
       </c>
       <c r="BC47" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1999-10-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>1999-10</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -7629,7 +8346,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -7649,7 +8366,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -7659,7 +8376,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d001/1995-1999.xlsx
+++ b/diseases/d001/1995-1999.xlsx
@@ -1938,6 +1938,11 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1950,12 +1955,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -2312,6 +2327,11 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2324,12 +2344,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2447,6 +2477,11 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2459,12 +2494,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2582,6 +2627,11 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2594,12 +2644,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2717,6 +2777,11 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2729,12 +2794,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2852,6 +2927,11 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2864,12 +2944,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2987,6 +3077,11 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2999,12 +3094,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3122,6 +3227,11 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3134,12 +3244,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3257,6 +3377,11 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3269,12 +3394,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3392,6 +3527,11 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3404,12 +3544,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3527,6 +3677,11 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3539,12 +3694,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3662,6 +3827,11 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3674,12 +3844,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -4187,6 +4367,11 @@
       <c r="Q23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4199,12 +4384,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4561,6 +4756,11 @@
       <c r="Q25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4573,12 +4773,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4696,6 +4906,11 @@
       <c r="Q26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4708,12 +4923,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4831,6 +5056,11 @@
       <c r="Q27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4843,12 +5073,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4966,6 +5206,11 @@
       <c r="Q28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4978,12 +5223,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5101,6 +5356,11 @@
       <c r="Q29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5113,12 +5373,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5236,6 +5506,11 @@
       <c r="Q30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5248,12 +5523,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5371,6 +5656,11 @@
       <c r="Q31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5383,12 +5673,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5506,6 +5806,11 @@
       <c r="Q32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5518,12 +5823,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5641,6 +5956,11 @@
       <c r="Q33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5653,12 +5973,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5776,6 +6106,11 @@
       <c r="Q34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5788,12 +6123,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5911,6 +6256,11 @@
       <c r="Q35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5923,12 +6273,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6436,6 +6796,11 @@
       <c r="Q38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6448,12 +6813,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6810,6 +7185,11 @@
       <c r="Q40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6822,12 +7202,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6945,6 +7335,11 @@
       <c r="Q41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6957,12 +7352,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7080,6 +7485,11 @@
       <c r="Q42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7092,12 +7502,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7215,6 +7635,11 @@
       <c r="Q43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7227,12 +7652,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7350,6 +7785,11 @@
       <c r="Q44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7362,12 +7802,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7485,6 +7935,11 @@
       <c r="Q45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7497,12 +7952,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7620,6 +8085,11 @@
       <c r="Q46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7632,12 +8102,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7755,6 +8235,11 @@
       <c r="Q47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7767,12 +8252,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7890,6 +8385,11 @@
       <c r="Q48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7902,12 +8402,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8025,6 +8535,11 @@
       <c r="Q49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8037,12 +8552,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8160,6 +8685,11 @@
       <c r="Q50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8172,12 +8702,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
